--- a/AAII_Financials/Yearly/MDRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MDRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>MDRX</t>
   </si>
@@ -684,22 +684,22 @@
         <v>45657</v>
       </c>
       <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
-      </c>
-      <c r="J7" s="2">
-        <v>43100</v>
       </c>
       <c r="K7" s="2">
         <v>42735</v>
@@ -729,22 +729,22 @@
         <v>594400</v>
       </c>
       <c r="E8" s="3">
+        <v>626000</v>
+      </c>
+      <c r="F8" s="3">
         <v>588000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>577400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>556100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1632600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1617800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1497700</v>
       </c>
       <c r="K8" s="3">
         <v>1386100</v>
@@ -774,22 +774,22 @@
         <v>292200</v>
       </c>
       <c r="E9" s="3">
+        <v>284500</v>
+      </c>
+      <c r="F9" s="3">
         <v>279600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>295000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>291900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>914500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>899800</v>
-      </c>
-      <c r="J9" s="3">
-        <v>780200</v>
       </c>
       <c r="K9" s="3">
         <v>713600</v>
@@ -819,22 +819,22 @@
         <v>302200</v>
       </c>
       <c r="E10" s="3">
+        <v>341500</v>
+      </c>
+      <c r="F10" s="3">
         <v>308400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>282400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>264200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>718200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>718100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>717500</v>
       </c>
       <c r="K10" s="3">
         <v>672500</v>
@@ -883,22 +883,22 @@
         <v>108300</v>
       </c>
       <c r="E12" s="3">
+        <v>97000</v>
+      </c>
+      <c r="F12" s="3">
         <v>97900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>84100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>78600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>245400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>258700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>202300</v>
       </c>
       <c r="K12" s="3">
         <v>178500</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>126400</v>
+        <v>124100</v>
       </c>
       <c r="E14" s="3">
-        <v>27900</v>
+        <v>-15400</v>
       </c>
       <c r="F14" s="3">
+        <v>27400</v>
+      </c>
+      <c r="G14" s="3">
         <v>-81400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>177200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-83400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>165300</v>
       </c>
       <c r="K14" s="3">
         <v>4700</v>
@@ -1018,22 +1018,22 @@
         <v>11000</v>
       </c>
       <c r="E15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F15" s="3">
         <v>60900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>135100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>123200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>102100</v>
       </c>
       <c r="K15" s="3">
         <v>87100</v>
@@ -1079,22 +1079,22 @@
         <v>680900</v>
       </c>
       <c r="E17" s="3">
-        <v>607100</v>
+        <v>591100</v>
       </c>
       <c r="F17" s="3">
+        <v>607600</v>
+      </c>
+      <c r="G17" s="3">
         <v>500100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>538000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1695800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1712900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1485200</v>
       </c>
       <c r="K17" s="3">
         <v>1313700</v>
@@ -1124,22 +1124,22 @@
         <v>-86400</v>
       </c>
       <c r="E18" s="3">
-        <v>-19100</v>
+        <v>34800</v>
       </c>
       <c r="F18" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="G18" s="3">
         <v>77300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-63200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-95100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>12500</v>
       </c>
       <c r="K18" s="3">
         <v>72400</v>
@@ -1185,22 +1185,22 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>10400</v>
+        <v>12700</v>
       </c>
       <c r="E20" s="3">
-        <v>17200</v>
+        <v>6600</v>
       </c>
       <c r="F20" s="3">
+        <v>15400</v>
+      </c>
+      <c r="G20" s="3">
         <v>-8500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-300</v>
       </c>
       <c r="J20" s="3">
         <v>-300</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-85800</v>
+        <v>-88100</v>
       </c>
       <c r="E21" s="3">
-        <v>24600</v>
+        <v>37000</v>
       </c>
       <c r="F21" s="3">
+        <v>25900</v>
+      </c>
+      <c r="G21" s="3">
         <v>95100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>47900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>73700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>114900</v>
       </c>
       <c r="K21" s="3">
         <v>152800</v>
@@ -1278,22 +1278,22 @@
         <v>15000</v>
       </c>
       <c r="E22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F22" s="3">
         <v>6400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>43200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>50900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>37500</v>
       </c>
       <c r="K22" s="3">
         <v>29500</v>
@@ -1323,22 +1323,22 @@
         <v>-222100</v>
       </c>
       <c r="E23" s="3">
+        <v>59900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-63900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>157700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-281800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-62200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-190000</v>
       </c>
       <c r="K23" s="3">
         <v>31600</v>
@@ -1368,22 +1368,22 @@
         <v>69500</v>
       </c>
       <c r="E24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F24" s="3">
         <v>-43800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>29900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-43300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-19000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-5500</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
@@ -1458,22 +1458,22 @@
         <v>-291600</v>
       </c>
       <c r="E26" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-20000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>127800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-238400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-43200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-184500</v>
       </c>
       <c r="K26" s="3">
         <v>31300</v>
@@ -1503,22 +1503,22 @@
         <v>-291500</v>
       </c>
       <c r="E27" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-86500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>139600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>696000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-182200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>363700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-196500</v>
       </c>
       <c r="K27" s="3">
         <v>-25600</v>
@@ -1593,22 +1593,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-66400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>11800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>723700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>55800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>402400</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-13500</v>
       </c>
       <c r="K29" s="3">
         <v>-56800</v>
@@ -1725,22 +1725,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-10400</v>
+        <v>-12700</v>
       </c>
       <c r="E32" s="3">
-        <v>-17200</v>
+        <v>-6600</v>
       </c>
       <c r="F32" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="G32" s="3">
         <v>8500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>300</v>
       </c>
       <c r="J32" s="3">
         <v>300</v>
@@ -1773,22 +1773,22 @@
         <v>-291500</v>
       </c>
       <c r="E33" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-86500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>139600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>696100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-182200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>363700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-196500</v>
       </c>
       <c r="K33" s="3">
         <v>-25700</v>
@@ -1863,22 +1863,22 @@
         <v>-291500</v>
       </c>
       <c r="E35" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-86500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>139600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>696100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-182200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>363700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-196500</v>
       </c>
       <c r="K35" s="3">
         <v>-25700</v>
@@ -1913,22 +1913,22 @@
         <v>45657</v>
       </c>
       <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
-      </c>
-      <c r="J38" s="2">
-        <v>43100</v>
       </c>
       <c r="K38" s="2">
         <v>42735</v>
@@ -1999,19 +1999,19 @@
         <v>446600</v>
       </c>
       <c r="F41" s="3">
+        <v>446600</v>
+      </c>
+      <c r="G41" s="3">
         <v>133700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>531100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>129700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>174200</v>
-      </c>
-      <c r="J41" s="3">
-        <v>119500</v>
       </c>
       <c r="K41" s="3">
         <v>95600</v>
@@ -2086,22 +2086,22 @@
         <v>198500</v>
       </c>
       <c r="E43" s="3">
+        <v>198500</v>
+      </c>
+      <c r="F43" s="3">
         <v>175700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>184900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>479500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>517700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>531700</v>
-      </c>
-      <c r="J43" s="3">
-        <v>492600</v>
       </c>
       <c r="K43" s="3">
         <v>405200</v>
@@ -2172,26 +2172,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>24</v>
+      <c r="D45" s="3">
+        <v>7200</v>
       </c>
       <c r="E45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>278200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>43800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>128200</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
@@ -2221,22 +2221,22 @@
         <v>545600</v>
       </c>
       <c r="E46" s="3">
+        <v>699200</v>
+      </c>
+      <c r="F46" s="3">
         <v>679600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>649200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1153200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>841300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>859000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>857100</v>
       </c>
       <c r="K46" s="3">
         <v>604300</v>
@@ -2266,22 +2266,22 @@
         <v>98700</v>
       </c>
       <c r="E47" s="3">
+        <v>98500</v>
+      </c>
+      <c r="F47" s="3">
         <v>58100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>56700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>35800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>37000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>30000</v>
       </c>
       <c r="K47" s="3">
         <v>178700</v>
@@ -2307,26 +2307,26 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>24</v>
+      <c r="D48" s="3">
+        <v>15400</v>
       </c>
       <c r="E48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F48" s="3">
         <v>21400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>168800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>183700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>121900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>135400</v>
       </c>
       <c r="K48" s="3">
         <v>148800</v>
@@ -2356,22 +2356,22 @@
         <v>671700</v>
       </c>
       <c r="E49" s="3">
+        <v>677300</v>
+      </c>
+      <c r="F49" s="3">
         <v>697000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>729200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1454500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1563900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2014500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1923200</v>
       </c>
       <c r="K49" s="3">
         <v>2829300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>35100</v>
+        <v>13900</v>
       </c>
       <c r="E52" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F52" s="3">
         <v>11300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>839900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>467800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>51400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1279900</v>
       </c>
       <c r="K52" s="3">
         <v>68200</v>
@@ -2581,22 +2581,22 @@
         <v>1352300</v>
       </c>
       <c r="E54" s="3">
+        <v>1572900</v>
+      </c>
+      <c r="F54" s="3">
         <v>1504700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2311000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2917600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3205700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3181500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>4230200</v>
       </c>
       <c r="K54" s="3">
         <v>3832200</v>
@@ -2664,22 +2664,22 @@
         <v>30900</v>
       </c>
       <c r="E57" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F57" s="3">
         <v>30800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>102800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>73200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>85700</v>
       </c>
       <c r="K57" s="3">
         <v>126100</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>154700</v>
+        <v>159200</v>
       </c>
       <c r="E58" s="3">
+        <v>208700</v>
+      </c>
+      <c r="F58" s="3">
         <v>6600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>386800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>28800</v>
       </c>
       <c r="K58" s="3">
         <v>26700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>154200</v>
+        <v>149600</v>
       </c>
       <c r="E59" s="3">
+        <v>136700</v>
+      </c>
+      <c r="F59" s="3">
         <v>109700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>409300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>657600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>530000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>497400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>614200</v>
       </c>
       <c r="K59" s="3">
         <v>363800</v>
@@ -2799,22 +2799,22 @@
         <v>421900</v>
       </c>
       <c r="E60" s="3">
+        <v>446000</v>
+      </c>
+      <c r="F60" s="3">
         <v>230300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>488400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>934800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1210700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>797700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>889600</v>
       </c>
       <c r="K60" s="3">
         <v>667100</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>72200</v>
+        <v>80300</v>
       </c>
       <c r="E61" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F61" s="3">
         <v>212800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>366800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>261100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>644600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>647500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>909100</v>
       </c>
       <c r="K61" s="3">
         <v>1304600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>54200</v>
+        <v>32900</v>
       </c>
       <c r="E62" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F62" s="3">
         <v>44100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>76500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>81300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>797400</v>
       </c>
       <c r="K62" s="3">
         <v>39800</v>
@@ -3069,22 +3069,22 @@
         <v>548300</v>
       </c>
       <c r="E66" s="3">
+        <v>498400</v>
+      </c>
+      <c r="F66" s="3">
         <v>487200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>950600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1251400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1920600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1601100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2638500</v>
       </c>
       <c r="K66" s="3">
         <v>2171300</v>
@@ -3313,22 +3313,22 @@
         <v>403400</v>
       </c>
       <c r="E72" s="3">
+        <v>695000</v>
+      </c>
+      <c r="F72" s="3">
         <v>645800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>719800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>633100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-49300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>132800</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-338200</v>
       </c>
       <c r="K72" s="3">
         <v>-187400</v>
@@ -3493,22 +3493,22 @@
         <v>804000</v>
       </c>
       <c r="E76" s="3">
+        <v>1074400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1017500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1360400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1666200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1285200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1551100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>1120900</v>
       </c>
       <c r="K76" s="3">
         <v>1232500</v>
@@ -3588,22 +3588,22 @@
         <v>45657</v>
       </c>
       <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
-      </c>
-      <c r="J80" s="2">
-        <v>43100</v>
       </c>
       <c r="K80" s="2">
         <v>42735</v>
@@ -3633,22 +3633,22 @@
         <v>-291500</v>
       </c>
       <c r="E81" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-86500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>139600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>696100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-182200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>363700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-196500</v>
       </c>
       <c r="K81" s="3">
         <v>-25700</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>45800</v>
+        <v>2300</v>
       </c>
       <c r="E83" s="3">
-        <v>9900</v>
+        <v>6100</v>
       </c>
       <c r="F83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G83" s="3">
         <v>12700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>40700</v>
       </c>
       <c r="K83" s="3">
         <v>35300</v>
@@ -3967,22 +3967,22 @@
         <v>-20000</v>
       </c>
       <c r="E89" s="3">
-        <v>115600</v>
+        <v>99500</v>
       </c>
       <c r="F89" s="3">
+        <v>116800</v>
+      </c>
+      <c r="G89" s="3">
         <v>-76600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-103700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>46300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>67900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>279400</v>
       </c>
       <c r="K89" s="3">
         <v>269000</v>
@@ -4031,22 +4031,22 @@
         <v>-1600</v>
       </c>
       <c r="E91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-38800</v>
       </c>
       <c r="K91" s="3">
         <v>-32100</v>
@@ -4166,22 +4166,22 @@
         <v>-125700</v>
       </c>
       <c r="E94" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="F94" s="3">
         <v>585100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1614200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-161100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>248000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-413000</v>
       </c>
       <c r="K94" s="3">
         <v>-1154000</v>
@@ -4410,22 +4410,22 @@
         <v>-6700</v>
       </c>
       <c r="E100" s="3">
-        <v>-444900</v>
+        <v>-12500</v>
       </c>
       <c r="F100" s="3">
+        <v>-446200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-258900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1108200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>67300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-293000</v>
-      </c>
-      <c r="J100" s="3">
-        <v>198600</v>
       </c>
       <c r="K100" s="3">
         <v>865300</v>
@@ -4454,23 +4454,23 @@
       <c r="D101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
-      </c>
-      <c r="J101" s="3">
-        <v>900</v>
       </c>
       <c r="K101" s="3">
         <v>-500</v>
@@ -4500,22 +4500,22 @@
         <v>-152300</v>
       </c>
       <c r="E102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F102" s="3">
         <v>256200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-348200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>402300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-47300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>65900</v>
       </c>
       <c r="K102" s="3">
         <v>-20300</v>
